--- a/beck_with_ols_vp_dbf.xlsx
+++ b/beck_with_ols_vp_dbf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michael.a.moon\J_BECK_BIRD_NECROPY_ID\JBECK_BIRD_NECROPY_ID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88F2295-DFB4-4E2A-BCC9-58D2A21DF25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82686B3D-CBC1-45C2-A306-FE791976353A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20004" yWindow="-17436" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3864" uniqueCount="651">
   <si>
     <t>DEBRIEFER</t>
   </si>
@@ -2000,6 +2000,18 @@
   <si>
     <t>Changed permit based on debriefed haul</t>
   </si>
+  <si>
+    <t>Permit and boat name not in cruise.  Observer sp code not in cruise. This observer was not deployed in 2007.  Not in cruise 10941 spcomp AIMEE	KAYE observer for provided cruise.</t>
+  </si>
+  <si>
+    <t>Permit changed based on ols_vessel_plant.</t>
+  </si>
+  <si>
+    <t>Cruise 11352 without permit 748. Observer not deployed in 2007. Permit to 3692</t>
+  </si>
+  <si>
+    <t>11362 without permit 748.  However, only  species code 857 exists in this cruise  for these haul numbers.  So these should be good. Permit to 3692</t>
+  </si>
 </sst>
 </file>
 
@@ -2008,7 +2020,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm\ AM/PM"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -2032,13 +2044,31 @@
       <color rgb="FFFF0000"/>
       <name val="Dialog"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2053,18 +2083,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2407,19 +2461,19 @@
   <dimension ref="A1:U488"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="60.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="60.453125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>639</v>
       </c>
       <c r="B2" t="s">
@@ -2483,47 +2537,47 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="116">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:21" s="6" customFormat="1" ht="116">
+      <c r="A3" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="9">
         <v>151</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="9">
         <v>81</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="9">
         <v>138</v>
       </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="1">
+      <c r="K3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="9">
         <v>853</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="9">
         <v>857</v>
       </c>
-      <c r="O3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="O3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2587,7 +2641,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>641</v>
       </c>
       <c r="B5" t="s">
@@ -2596,13 +2650,13 @@
       <c r="C5" s="3">
         <v>36651</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>3</v>
       </c>
       <c r="G5" s="1">
         <v>6141</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>1695</v>
       </c>
       <c r="I5" t="s">
@@ -2643,7 +2697,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>643</v>
       </c>
       <c r="B6" t="s">
@@ -2652,13 +2706,13 @@
       <c r="C6" s="3">
         <v>38270</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>3</v>
       </c>
       <c r="G6" s="1">
         <v>9296</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>3339</v>
       </c>
       <c r="I6" t="s">
@@ -3168,13 +3222,13 @@
       <c r="C15" s="3">
         <v>38969</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>3</v>
       </c>
       <c r="G15" s="1">
         <v>10658</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>3339</v>
       </c>
       <c r="I15" t="s">
@@ -3274,7 +3328,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>644</v>
       </c>
       <c r="B17" t="s">
@@ -3283,13 +3337,13 @@
       <c r="C17" s="3">
         <v>38937</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="G17" s="1">
         <v>10674</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>3896</v>
       </c>
       <c r="I17" t="s">
@@ -3683,70 +3737,73 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:21" s="6" customFormat="1">
+      <c r="A24" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="8">
         <v>38937</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="9">
         <v>10722</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="9">
         <v>4769</v>
       </c>
-      <c r="J24" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" t="s">
-        <v>20</v>
-      </c>
-      <c r="M24" t="s">
-        <v>20</v>
-      </c>
-      <c r="N24" s="1">
+      <c r="J24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" s="9">
         <v>857</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O24" s="9">
         <v>8</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="9">
         <v>28</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="9">
         <v>2006</v>
       </c>
-      <c r="R24" t="s">
+      <c r="R24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="T24" t="s">
+      <c r="T24" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="U24" t="s">
+      <c r="U24" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:21">
+      <c r="A25" s="4" t="s">
+        <v>648</v>
+      </c>
       <c r="B25" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="3">
         <v>38937</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>3</v>
       </c>
       <c r="G25" s="1">
         <v>10734</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>4533</v>
       </c>
       <c r="I25" t="s">
@@ -3787,7 +3844,7 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B26" t="s">
@@ -3796,13 +3853,13 @@
       <c r="C26" s="3">
         <v>38969</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>3</v>
       </c>
       <c r="G26" s="1">
         <v>10736</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="5">
         <v>3385</v>
       </c>
       <c r="I26" t="s">
@@ -4196,7 +4253,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="2:21">
+    <row r="33" spans="1:21">
       <c r="B33" t="s">
         <v>35</v>
       </c>
@@ -4255,7 +4312,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="2:21">
+    <row r="34" spans="1:21">
       <c r="B34" t="s">
         <v>35</v>
       </c>
@@ -4314,18 +4371,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="2:21">
+    <row r="35" spans="1:21">
       <c r="B35" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="3">
         <v>39083</v>
       </c>
+      <c r="D35" s="4">
+        <v>3</v>
+      </c>
       <c r="G35" s="1">
         <v>10927</v>
       </c>
-      <c r="H35" s="1">
-        <v>4197</v>
+      <c r="H35" s="5">
+        <v>1276</v>
       </c>
       <c r="I35" t="s">
         <v>99</v>
@@ -4364,7 +4424,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="2:21">
+    <row r="36" spans="1:21">
       <c r="B36" t="s">
         <v>30</v>
       </c>
@@ -4423,7 +4483,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="2:21">
+    <row r="37" spans="1:21">
       <c r="B37" t="s">
         <v>30</v>
       </c>
@@ -4482,57 +4542,60 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="2:21">
-      <c r="B38" t="s">
+    <row r="38" spans="1:21" s="6" customFormat="1">
+      <c r="A38" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="8">
         <v>39083</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="9">
         <v>10941</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="9">
         <v>3308</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="J38" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M38" s="1">
+      <c r="J38" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="9">
         <v>874</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N38" s="9">
         <v>879</v>
       </c>
-      <c r="O38" s="1">
+      <c r="O38" s="9">
         <v>1</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="9">
         <v>4</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="9">
         <v>2007</v>
       </c>
-      <c r="R38" t="s">
+      <c r="R38" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="T38" t="s">
+      <c r="T38" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="U38" t="s">
+      <c r="U38" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="2:21">
+    <row r="39" spans="1:21">
       <c r="B39" t="s">
         <v>30</v>
       </c>
@@ -4591,7 +4654,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="2:21">
+    <row r="40" spans="1:21">
       <c r="B40" t="s">
         <v>75</v>
       </c>
@@ -4650,7 +4713,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="2:21">
+    <row r="41" spans="1:21">
       <c r="B41" t="s">
         <v>72</v>
       </c>
@@ -4709,7 +4772,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="2:21">
+    <row r="42" spans="1:21">
       <c r="B42" t="s">
         <v>72</v>
       </c>
@@ -4768,7 +4831,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="2:21">
+    <row r="43" spans="1:21">
       <c r="B43" t="s">
         <v>72</v>
       </c>
@@ -4827,7 +4890,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="2:21">
+    <row r="44" spans="1:21">
       <c r="B44" t="s">
         <v>30</v>
       </c>
@@ -4886,7 +4949,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="2:21">
+    <row r="45" spans="1:21">
       <c r="B45" t="s">
         <v>30</v>
       </c>
@@ -4945,7 +5008,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="2:21">
+    <row r="46" spans="1:21">
       <c r="B46" t="s">
         <v>58</v>
       </c>
@@ -5004,7 +5067,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="2:21">
+    <row r="47" spans="1:21">
       <c r="B47" t="s">
         <v>58</v>
       </c>
@@ -5063,7 +5126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="2:21">
+    <row r="48" spans="1:21">
       <c r="B48" t="s">
         <v>116</v>
       </c>
@@ -5122,7 +5185,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:21">
+    <row r="49" spans="1:21">
       <c r="B49" t="s">
         <v>116</v>
       </c>
@@ -5181,7 +5244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:21">
+    <row r="50" spans="1:21">
       <c r="B50" t="s">
         <v>116</v>
       </c>
@@ -5240,7 +5303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="2:21">
+    <row r="51" spans="1:21">
       <c r="B51" t="s">
         <v>116</v>
       </c>
@@ -5299,7 +5362,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="2:21">
+    <row r="52" spans="1:21">
       <c r="B52" t="s">
         <v>122</v>
       </c>
@@ -5358,7 +5421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="2:21">
+    <row r="53" spans="1:21">
       <c r="B53" t="s">
         <v>35</v>
       </c>
@@ -5417,7 +5480,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="2:21">
+    <row r="54" spans="1:21">
       <c r="B54" t="s">
         <v>58</v>
       </c>
@@ -5476,7 +5539,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="2:21">
+    <row r="55" spans="1:21">
       <c r="B55" t="s">
         <v>58</v>
       </c>
@@ -5535,7 +5598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="2:21">
+    <row r="56" spans="1:21">
       <c r="B56" t="s">
         <v>35</v>
       </c>
@@ -5594,403 +5657,427 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="2:21">
-      <c r="B57" t="s">
+    <row r="57" spans="1:21" s="17" customFormat="1">
+      <c r="A57" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="B57" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="18">
         <v>39302</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G57" s="19">
         <v>11352</v>
       </c>
-      <c r="H57" s="1">
-        <v>748</v>
-      </c>
-      <c r="I57" t="s">
+      <c r="H57" s="20">
+        <v>3692</v>
+      </c>
+      <c r="I57" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57" s="19">
         <v>21</v>
       </c>
-      <c r="K57" t="s">
-        <v>20</v>
-      </c>
-      <c r="L57" t="s">
-        <v>20</v>
-      </c>
-      <c r="M57" t="s">
-        <v>20</v>
-      </c>
-      <c r="N57" s="1">
+      <c r="K57" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N57" s="19">
         <v>857</v>
       </c>
-      <c r="O57" s="1">
+      <c r="O57" s="19">
         <v>8</v>
       </c>
-      <c r="P57" s="1">
-        <v>20</v>
-      </c>
-      <c r="Q57" s="1">
+      <c r="P57" s="19">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="19">
         <v>2007</v>
       </c>
-      <c r="R57" t="s">
+      <c r="R57" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="T57" t="s">
+      <c r="T57" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="U57" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="2:21">
-      <c r="B58" t="s">
+      <c r="U57" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" s="17" customFormat="1">
+      <c r="A58" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="B58" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="18">
         <v>39302</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" s="19">
         <v>11352</v>
       </c>
-      <c r="H58" s="1">
-        <v>748</v>
-      </c>
-      <c r="I58" t="s">
+      <c r="H58" s="20">
+        <v>3692</v>
+      </c>
+      <c r="I58" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J58" s="19">
         <v>30</v>
       </c>
-      <c r="K58" t="s">
-        <v>20</v>
-      </c>
-      <c r="L58" t="s">
-        <v>20</v>
-      </c>
-      <c r="M58" t="s">
-        <v>20</v>
-      </c>
-      <c r="N58" s="1">
+      <c r="K58" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M58" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N58" s="19">
         <v>857</v>
       </c>
-      <c r="O58" s="1">
+      <c r="O58" s="19">
         <v>8</v>
       </c>
-      <c r="P58" s="1">
+      <c r="P58" s="19">
         <v>22</v>
       </c>
-      <c r="Q58" s="1">
+      <c r="Q58" s="19">
         <v>2007</v>
       </c>
-      <c r="R58" t="s">
+      <c r="R58" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="T58" t="s">
+      <c r="T58" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="U58" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="2:21">
-      <c r="B59" t="s">
+      <c r="U58" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" s="17" customFormat="1">
+      <c r="A59" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="B59" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="18">
         <v>39302</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="19">
         <v>11352</v>
       </c>
-      <c r="H59" s="1">
-        <v>748</v>
-      </c>
-      <c r="I59" t="s">
+      <c r="H59" s="20">
+        <v>3692</v>
+      </c>
+      <c r="I59" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59" s="19">
         <v>32</v>
       </c>
-      <c r="K59" t="s">
-        <v>20</v>
-      </c>
-      <c r="L59" t="s">
-        <v>20</v>
-      </c>
-      <c r="M59" t="s">
-        <v>20</v>
-      </c>
-      <c r="N59" s="1">
+      <c r="K59" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L59" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M59" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N59" s="19">
         <v>857</v>
       </c>
-      <c r="O59" s="1">
+      <c r="O59" s="19">
         <v>8</v>
       </c>
-      <c r="P59" s="1">
-        <v>23</v>
-      </c>
-      <c r="Q59" s="1">
+      <c r="P59" s="19">
+        <v>23</v>
+      </c>
+      <c r="Q59" s="19">
         <v>2007</v>
       </c>
-      <c r="R59" t="s">
+      <c r="R59" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="T59" t="s">
+      <c r="T59" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="U59" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="2:21">
-      <c r="B60" t="s">
+      <c r="U59" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" s="17" customFormat="1">
+      <c r="A60" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="B60" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="18">
         <v>39302</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60" s="19">
         <v>11352</v>
       </c>
-      <c r="H60" s="1">
-        <v>748</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="H60" s="20">
+        <v>3692</v>
+      </c>
+      <c r="I60" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J60" s="19">
         <v>37</v>
       </c>
-      <c r="K60" t="s">
-        <v>20</v>
-      </c>
-      <c r="L60" t="s">
-        <v>20</v>
-      </c>
-      <c r="M60" t="s">
-        <v>20</v>
-      </c>
-      <c r="N60" s="1">
+      <c r="K60" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M60" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N60" s="19">
         <v>857</v>
       </c>
-      <c r="O60" s="1">
+      <c r="O60" s="19">
         <v>8</v>
       </c>
-      <c r="P60" s="1">
+      <c r="P60" s="19">
         <v>24</v>
       </c>
-      <c r="Q60" s="1">
+      <c r="Q60" s="19">
         <v>2007</v>
       </c>
-      <c r="R60" t="s">
+      <c r="R60" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="T60" t="s">
+      <c r="T60" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="U60" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" spans="2:21">
-      <c r="B61" t="s">
+      <c r="U60" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" s="12" customFormat="1">
+      <c r="A61" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B61" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="13">
         <v>39302</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G61" s="14">
         <v>11362</v>
       </c>
-      <c r="H61" s="1">
-        <v>748</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="H61" s="15">
+        <v>3692</v>
+      </c>
+      <c r="I61" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J61" s="14">
         <v>346</v>
       </c>
-      <c r="K61" t="s">
-        <v>20</v>
-      </c>
-      <c r="L61" t="s">
-        <v>20</v>
-      </c>
-      <c r="M61" t="s">
-        <v>20</v>
-      </c>
-      <c r="N61" s="1">
+      <c r="K61" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M61" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N61" s="14">
         <v>857</v>
       </c>
-      <c r="O61" s="1">
+      <c r="O61" s="14">
         <v>8</v>
       </c>
-      <c r="P61" s="1">
+      <c r="P61" s="14">
         <v>3</v>
       </c>
-      <c r="Q61" s="1">
+      <c r="Q61" s="14">
         <v>2007</v>
       </c>
-      <c r="R61" t="s">
+      <c r="R61" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="T61" t="s">
+      <c r="T61" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="U61" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="2:21">
-      <c r="B62" t="s">
+      <c r="U61" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" s="12" customFormat="1">
+      <c r="A62" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B62" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="13">
         <v>39302</v>
       </c>
-      <c r="G62" s="1">
+      <c r="G62" s="14">
         <v>11362</v>
       </c>
-      <c r="H62" s="1">
-        <v>748</v>
-      </c>
-      <c r="I62" t="s">
+      <c r="H62" s="15">
+        <v>3692</v>
+      </c>
+      <c r="I62" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62" s="14">
         <v>367</v>
       </c>
-      <c r="K62" t="s">
-        <v>20</v>
-      </c>
-      <c r="L62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M62" t="s">
-        <v>20</v>
-      </c>
-      <c r="N62" s="1">
+      <c r="K62" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L62" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M62" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N62" s="14">
         <v>857</v>
       </c>
-      <c r="O62" s="1">
+      <c r="O62" s="14">
         <v>8</v>
       </c>
-      <c r="P62" s="1">
+      <c r="P62" s="14">
         <v>8</v>
       </c>
-      <c r="Q62" s="1">
+      <c r="Q62" s="14">
         <v>2007</v>
       </c>
-      <c r="R62" t="s">
+      <c r="R62" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="T62" t="s">
+      <c r="T62" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="U62" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" spans="2:21">
-      <c r="B63" t="s">
+      <c r="U62" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" s="12" customFormat="1">
+      <c r="A63" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="13">
         <v>39302</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G63" s="14">
         <v>11362</v>
       </c>
-      <c r="H63" s="1">
-        <v>748</v>
-      </c>
-      <c r="I63" t="s">
+      <c r="H63" s="15">
+        <v>3692</v>
+      </c>
+      <c r="I63" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J63" s="14">
         <v>367</v>
       </c>
-      <c r="K63" t="s">
-        <v>20</v>
-      </c>
-      <c r="L63" t="s">
-        <v>20</v>
-      </c>
-      <c r="M63" t="s">
-        <v>20</v>
-      </c>
-      <c r="N63" s="1">
+      <c r="K63" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N63" s="14">
         <v>857</v>
       </c>
-      <c r="O63" s="1">
+      <c r="O63" s="14">
         <v>8</v>
       </c>
-      <c r="P63" s="1">
+      <c r="P63" s="14">
         <v>8</v>
       </c>
-      <c r="Q63" s="1">
+      <c r="Q63" s="14">
         <v>2007</v>
       </c>
-      <c r="R63" t="s">
+      <c r="R63" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="T63" t="s">
+      <c r="T63" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="U63" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="2:21">
-      <c r="B64" t="s">
+      <c r="U63" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" s="12" customFormat="1">
+      <c r="A64" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B64" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="13">
         <v>39302</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G64" s="14">
         <v>11362</v>
       </c>
-      <c r="H64" s="1">
-        <v>748</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="H64" s="15">
+        <v>3692</v>
+      </c>
+      <c r="I64" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64" s="14">
         <v>367</v>
       </c>
-      <c r="K64" t="s">
-        <v>20</v>
-      </c>
-      <c r="L64" t="s">
-        <v>20</v>
-      </c>
-      <c r="M64" t="s">
-        <v>20</v>
-      </c>
-      <c r="N64" s="1">
+      <c r="K64" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M64" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N64" s="14">
         <v>857</v>
       </c>
-      <c r="O64" s="1">
+      <c r="O64" s="14">
         <v>8</v>
       </c>
-      <c r="P64" s="1">
+      <c r="P64" s="14">
         <v>8</v>
       </c>
-      <c r="Q64" s="1">
+      <c r="Q64" s="14">
         <v>2007</v>
       </c>
-      <c r="R64" t="s">
+      <c r="R64" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="T64" t="s">
+      <c r="T64" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="U64" t="s">
+      <c r="U64" s="12" t="s">
         <v>23</v>
       </c>
     </row>
@@ -29715,7 +29802,9 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/beck_with_ols_vp_dbf.xlsx
+++ b/beck_with_ols_vp_dbf.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michael.a.moon\J_BECK_BIRD_NECROPY_ID\JBECK_BIRD_NECROPY_ID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82686B3D-CBC1-45C2-A306-FE791976353A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0AE685-28B8-4794-9BE6-C695B0418449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20004" yWindow="-17436" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13410" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Worksheet" sheetId="1" r:id="rId1"/>
     <sheet name="SQL" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3864" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3864" uniqueCount="652">
   <si>
     <t>DEBRIEFER</t>
   </si>
@@ -2011,6 +2024,9 @@
   </si>
   <si>
     <t>11362 without permit 748.  However, only  species code 857 exists in this cruise  for these haul numbers.  So these should be good. Permit to 3692</t>
+  </si>
+  <si>
+    <t>Added permit.</t>
   </si>
 </sst>
 </file>
@@ -6081,7 +6097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="2:21">
+    <row r="65" spans="1:21">
       <c r="B65" t="s">
         <v>116</v>
       </c>
@@ -6140,7 +6156,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="2:21">
+    <row r="66" spans="1:21">
       <c r="B66" t="s">
         <v>130</v>
       </c>
@@ -6199,7 +6215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="2:21">
+    <row r="67" spans="1:21">
       <c r="B67" t="s">
         <v>144</v>
       </c>
@@ -6258,7 +6274,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="2:21">
+    <row r="68" spans="1:21">
       <c r="B68" t="s">
         <v>144</v>
       </c>
@@ -6317,7 +6333,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="2:21">
+    <row r="69" spans="1:21">
       <c r="B69" t="s">
         <v>144</v>
       </c>
@@ -6376,7 +6392,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="2:21">
+    <row r="70" spans="1:21">
       <c r="B70" t="s">
         <v>144</v>
       </c>
@@ -6435,7 +6451,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="2:21">
+    <row r="71" spans="1:21">
       <c r="B71" t="s">
         <v>144</v>
       </c>
@@ -6494,7 +6510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="2:21">
+    <row r="72" spans="1:21">
       <c r="B72" t="s">
         <v>144</v>
       </c>
@@ -6553,7 +6569,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="2:21">
+    <row r="73" spans="1:21">
       <c r="B73" t="s">
         <v>144</v>
       </c>
@@ -6612,7 +6628,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="2:21">
+    <row r="74" spans="1:21">
+      <c r="A74" s="4" t="s">
+        <v>651</v>
+      </c>
       <c r="B74" t="s">
         <v>144</v>
       </c>
@@ -6622,8 +6641,8 @@
       <c r="G74" s="1">
         <v>11388</v>
       </c>
-      <c r="H74" t="s">
-        <v>20</v>
+      <c r="H74" s="5">
+        <v>2090</v>
       </c>
       <c r="J74" s="1">
         <v>99</v>
@@ -6659,7 +6678,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="2:21">
+    <row r="75" spans="1:21">
       <c r="B75" t="s">
         <v>154</v>
       </c>
@@ -6718,7 +6737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="2:21">
+    <row r="76" spans="1:21">
       <c r="B76" t="s">
         <v>154</v>
       </c>
@@ -6777,7 +6796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="2:21">
+    <row r="77" spans="1:21">
       <c r="B77" t="s">
         <v>154</v>
       </c>
@@ -6836,7 +6855,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="2:21">
+    <row r="78" spans="1:21">
       <c r="B78" t="s">
         <v>154</v>
       </c>
@@ -6895,7 +6914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="2:21">
+    <row r="79" spans="1:21">
       <c r="B79" t="s">
         <v>154</v>
       </c>
@@ -6954,7 +6973,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="2:21">
+    <row r="80" spans="1:21">
       <c r="B80" t="s">
         <v>122</v>
       </c>
@@ -7727,6 +7746,9 @@
       </c>
       <c r="C93" s="3">
         <v>39334</v>
+      </c>
+      <c r="D93" s="4">
+        <v>2</v>
       </c>
       <c r="G93" s="1">
         <v>11452</v>
